--- a/data-manipulation-scripts/sheets-cleanup/sheets/COMBUSTIVEL - 20_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/COMBUSTIVEL - 20_01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -28,7 +28,7 @@
     <t>0751320983350</t>
   </si>
   <si>
-    <t>BOMBA COMBUSTIVEL IRON GG160 182293</t>
+    <t>BOMBA COMBUSTIVEL IRON GG160 2016 A 2023 182293</t>
   </si>
   <si>
     <t>0751320978837</t>
@@ -64,31 +64,13 @@
     <t>7895099125665</t>
   </si>
   <si>
-    <t>BOMBA COMBUSTIVEL IRON FAZER250 027478</t>
+    <t>BOMBA COMBUSTIVEL IRON FAZER250 2018 A 2023 027478</t>
   </si>
   <si>
     <t>1160612345674</t>
   </si>
   <si>
     <t>BOMBA COMBUSTIVEL EMBUS POP110I 2016 A 2017 11606E</t>
-  </si>
-  <si>
-    <t>7898616000018</t>
-  </si>
-  <si>
-    <t>BOIA TANQUE BHD SUSUKI YES125 2006 A 2008</t>
-  </si>
-  <si>
-    <t>7899761405482</t>
-  </si>
-  <si>
-    <t>BOIA TANQUE MAGNETRON FAN CG125</t>
-  </si>
-  <si>
-    <t>7898508618543</t>
-  </si>
-  <si>
-    <t>BOIA TANQUE FLEX MAGNETRON CG FAN TITAN150 2010 EM DIANTE</t>
   </si>
   <si>
     <t>7898635123163</t>
@@ -101,30 +83,6 @@
   </si>
   <si>
     <t>BOMBA COMBUSTIVEL SMARTFOX BIZ125 2009 A 2010</t>
-  </si>
-  <si>
-    <t>0618341649910</t>
-  </si>
-  <si>
-    <t>BOIA TANQUE IRON XRE300 2012 189084</t>
-  </si>
-  <si>
-    <t>7908253800817</t>
-  </si>
-  <si>
-    <t>BOIA TANQUE TMAC CB300R 2009 A 2012</t>
-  </si>
-  <si>
-    <t>0602883769052</t>
-  </si>
-  <si>
-    <t>BOIA TANQUE IRON CB300 2012 189073</t>
-  </si>
-  <si>
-    <t>7908073720548</t>
-  </si>
-  <si>
-    <t>BOIA TANQUE SMARTFOX BROS NXR150 2009 A 2010</t>
   </si>
   <si>
     <t>7895099120356</t>
@@ -143,18 +101,6 @@
   </si>
   <si>
     <t>BOMBA COMBUSTIVEL FLEX IRON FAN TITAN CG150 2001 A 2013 23649</t>
-  </si>
-  <si>
-    <t>6941655633806</t>
-  </si>
-  <si>
-    <t>BOIA TANQUE ALLEN SUSUKI YES125 72336</t>
-  </si>
-  <si>
-    <t>751320976369</t>
-  </si>
-  <si>
-    <t>BOIA TANQUE IRON JET125 WUYANG 122459</t>
   </si>
 </sst>
 </file>
@@ -456,7 +402,9 @@
       <c r="C2" s="3">
         <v>1.0</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="3">
+        <v>320.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -468,7 +416,9 @@
       <c r="C3" s="3">
         <v>3.0</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="3">
+        <v>315.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
@@ -480,7 +430,9 @@
       <c r="C4" s="3">
         <v>1.0</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="3">
+        <v>450.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
@@ -492,7 +444,9 @@
       <c r="C5" s="3">
         <v>1.0</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="3">
+        <v>270.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
@@ -504,7 +458,9 @@
       <c r="C6" s="3">
         <v>1.0</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="3">
+        <v>290.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
@@ -516,7 +472,9 @@
       <c r="C7" s="3">
         <v>1.0</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="3">
+        <v>398.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
@@ -528,7 +486,9 @@
       <c r="C8" s="3">
         <v>1.0</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="3">
+        <v>300.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
@@ -538,7 +498,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D9" s="4"/>
     </row>
@@ -552,7 +512,9 @@
       <c r="C10" s="3">
         <v>1.0</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="3">
+        <v>460.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
@@ -564,7 +526,9 @@
       <c r="C11" s="3">
         <v>1.0</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="3">
+        <v>384.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
@@ -576,7 +540,9 @@
       <c r="C12" s="3">
         <v>1.0</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="3">
+        <v>320.0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
@@ -589,7 +555,7 @@
         <v>1.0</v>
       </c>
       <c r="D13" s="3">
-        <v>460.0</v>
+        <v>425.0</v>
       </c>
     </row>
     <row r="14">
@@ -602,117 +568,61 @@
       <c r="C14" s="3">
         <v>1.0</v>
       </c>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D17" s="3">
-        <v>460.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D18" s="3">
-        <v>65.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D21" s="3">
+      <c r="D14" s="3">
         <v>400.0</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+    </row>
     <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="3">
-        <v>1.0</v>
-      </c>
+      <c r="A22" s="5"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
       <c r="D22" s="4"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="A23" s="5"/>
+      <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
@@ -6518,66 +6428,6 @@
       <c r="C990" s="4"/>
       <c r="D990" s="4"/>
     </row>
-    <row r="991">
-      <c r="A991" s="5"/>
-      <c r="B991" s="4"/>
-      <c r="C991" s="4"/>
-      <c r="D991" s="4"/>
-    </row>
-    <row r="992">
-      <c r="A992" s="5"/>
-      <c r="B992" s="4"/>
-      <c r="C992" s="4"/>
-      <c r="D992" s="4"/>
-    </row>
-    <row r="993">
-      <c r="A993" s="5"/>
-      <c r="B993" s="4"/>
-      <c r="C993" s="4"/>
-      <c r="D993" s="4"/>
-    </row>
-    <row r="994">
-      <c r="A994" s="5"/>
-      <c r="B994" s="4"/>
-      <c r="C994" s="4"/>
-      <c r="D994" s="4"/>
-    </row>
-    <row r="995">
-      <c r="A995" s="5"/>
-      <c r="B995" s="4"/>
-      <c r="C995" s="4"/>
-      <c r="D995" s="4"/>
-    </row>
-    <row r="996">
-      <c r="A996" s="5"/>
-      <c r="B996" s="4"/>
-      <c r="C996" s="4"/>
-      <c r="D996" s="4"/>
-    </row>
-    <row r="997">
-      <c r="A997" s="5"/>
-      <c r="B997" s="4"/>
-      <c r="C997" s="4"/>
-      <c r="D997" s="4"/>
-    </row>
-    <row r="998">
-      <c r="A998" s="5"/>
-      <c r="B998" s="4"/>
-      <c r="C998" s="4"/>
-      <c r="D998" s="4"/>
-    </row>
-    <row r="999">
-      <c r="A999" s="5"/>
-      <c r="B999" s="4"/>
-      <c r="C999" s="4"/>
-      <c r="D999" s="4"/>
-    </row>
-    <row r="1000">
-      <c r="A1000" s="5"/>
-      <c r="B1000" s="4"/>
-      <c r="C1000" s="4"/>
-      <c r="D1000" s="4"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
